--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,410 +413,1457 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>16.80528</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.58728</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.74519</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.03664</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05066</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.81579</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.91239</v>
+        <v>16.8434</v>
       </c>
       <c r="D3" t="n">
-        <v>16.5195</v>
+        <v>16.5864</v>
       </c>
       <c r="E3" t="n">
-        <v>16.73543</v>
+        <v>16.75044</v>
       </c>
       <c r="F3" t="n">
-        <v>43.31925</v>
+        <v>42.50395</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05167</v>
+        <v>0.0504</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8597</v>
+        <v>1.78515</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.70612</v>
+        <v>16.63938</v>
       </c>
       <c r="D4" t="n">
-        <v>16.49045</v>
+        <v>16.5121</v>
       </c>
       <c r="E4" t="n">
-        <v>16.42878</v>
+        <v>16.54893</v>
       </c>
       <c r="F4" t="n">
-        <v>42.36552</v>
+        <v>43.40556</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05072</v>
+        <v>0.05018</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82862</v>
+        <v>1.81601</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.7302</v>
+        <v>16.86259</v>
       </c>
       <c r="D5" t="n">
-        <v>16.79891</v>
+        <v>16.65655</v>
       </c>
       <c r="E5" t="n">
-        <v>16.66013</v>
+        <v>16.77835</v>
       </c>
       <c r="F5" t="n">
-        <v>42.85069</v>
+        <v>42.69817</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05074</v>
+        <v>0.05104</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82229</v>
+        <v>1.82336</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.88828</v>
+        <v>16.99985</v>
       </c>
       <c r="D6" t="n">
-        <v>16.58909</v>
+        <v>16.73161</v>
       </c>
       <c r="E6" t="n">
-        <v>16.8464</v>
+        <v>16.82752</v>
       </c>
       <c r="F6" t="n">
-        <v>42.15067</v>
+        <v>43.42686</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05034</v>
+        <v>0.05179</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8354</v>
+        <v>1.84898</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.80608</v>
+        <v>16.89779</v>
       </c>
       <c r="D7" t="n">
-        <v>16.27023</v>
+        <v>16.1619</v>
       </c>
       <c r="E7" t="n">
-        <v>16.47527</v>
+        <v>16.38821</v>
       </c>
       <c r="F7" t="n">
-        <v>42.94684</v>
+        <v>42.35673</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05097</v>
+        <v>0.0509</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84485</v>
+        <v>1.81219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.81933</v>
+        <v>17.0618</v>
       </c>
       <c r="D8" t="n">
-        <v>16.6933</v>
+        <v>16.39174</v>
       </c>
       <c r="E8" t="n">
-        <v>17.1859</v>
+        <v>16.69824</v>
       </c>
       <c r="F8" t="n">
-        <v>42.94274</v>
+        <v>41.97002</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0502</v>
+        <v>0.05145</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83133</v>
+        <v>1.78616</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.85217</v>
+        <v>17.21522</v>
       </c>
       <c r="D9" t="n">
-        <v>16.47811</v>
+        <v>16.14815</v>
       </c>
       <c r="E9" t="n">
-        <v>16.39466</v>
+        <v>16.77696</v>
       </c>
       <c r="F9" t="n">
-        <v>42.49565</v>
+        <v>42.41325</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05146</v>
+        <v>0.05004</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82091</v>
+        <v>1.77152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.50925</v>
+        <v>16.94553</v>
       </c>
       <c r="D10" t="n">
-        <v>16.89468</v>
+        <v>16.64901</v>
       </c>
       <c r="E10" t="n">
-        <v>16.31944</v>
+        <v>16.9035</v>
       </c>
       <c r="F10" t="n">
-        <v>41.96845</v>
+        <v>42.07463</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05133</v>
+        <v>0.04961</v>
       </c>
       <c r="H10" t="n">
-        <v>1.79711</v>
+        <v>1.86188</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.80542</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.58728</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.92264</v>
-      </c>
-      <c r="F11" t="n">
-        <v>42.43009</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05034</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.80995</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16.89688</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.42365</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.718</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.20147</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05123</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.83122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60466</v>
+        <v>16.78694</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10797</v>
+        <v>16.55305</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.64595</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.01744</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05039</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.82174</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.62072</v>
+        <v>16.7544</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11598</v>
+        <v>16.50368</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.55402</v>
+      </c>
+      <c r="F14" t="n">
+        <v>41.40597</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.79904</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6172299999999999</v>
+        <v>16.84788</v>
       </c>
       <c r="D15" t="n">
-        <v>1.11615</v>
+        <v>16.4431</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.83794</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.42595</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.83279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.59742</v>
+        <v>16.53656</v>
       </c>
       <c r="D16" t="n">
-        <v>1.08798</v>
+        <v>16.32134</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.49444</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41.94534</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.76014</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.60236</v>
+        <v>16.73945</v>
       </c>
       <c r="D17" t="n">
-        <v>1.12638</v>
+        <v>16.44091</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.56168</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43.21421</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05124</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.83773</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.61166</v>
+        <v>17.29601</v>
       </c>
       <c r="D18" t="n">
-        <v>1.11696</v>
+        <v>16.27851</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.57686</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.39711</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84008</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.61935</v>
+        <v>16.76458</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12655</v>
+        <v>16.63754</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.75397</v>
+      </c>
+      <c r="F19" t="n">
+        <v>41.35535</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.80084</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16.80787</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.19797</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.66423</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.49757</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05047</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.81707</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15.66964</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.48696</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.66619</v>
+      </c>
+      <c r="F22" t="n">
+        <v>249.01817</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.55583</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.2062</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.41787</v>
+      </c>
+      <c r="F23" t="n">
+        <v>254.34331</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15.87189</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.50295</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.54399</v>
+      </c>
+      <c r="F24" t="n">
+        <v>254.75954</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15.75794</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.56738</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.642</v>
+      </c>
+      <c r="F25" t="n">
+        <v>258.34311</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15.68941</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.5051</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.52523</v>
+      </c>
+      <c r="F26" t="n">
+        <v>257.91328</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15.62859</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.26157</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.62797</v>
+      </c>
+      <c r="F27" t="n">
+        <v>255.4709</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15.69948</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.31473</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.51023</v>
+      </c>
+      <c r="F28" t="n">
+        <v>251.92626</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0.60015</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.0966</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="C29" t="n">
+        <v>15.67014</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.46405</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.55569</v>
+      </c>
+      <c r="F29" t="n">
+        <v>251.99311</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.11509</v>
+      <c r="C30" t="n">
+        <v>15.82088</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.53896</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.65982</v>
+      </c>
+      <c r="F30" t="n">
+        <v>254.67731</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.88577</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.16864</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.38949</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.60815</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.11922</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.82303</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.89103</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.53638</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.52669</v>
+      </c>
+      <c r="G33" t="n">
+        <v>33.98285</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.61128</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15.73546</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.29342</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.39803</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.66305</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.67401</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.05165</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.10124</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.90405</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.61104</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.63002</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.18591</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.52843</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.19975</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.41731</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.01702</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.70018</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.19509</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.55625</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.22094</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.35347</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.86509</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.20056</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.4365</v>
+      </c>
+      <c r="G38" t="n">
+        <v>33.68333</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.75198</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.06439</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.50118</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.76089</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.26083</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.95882</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.09794</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.24916</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.66927</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.67468</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.62127</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.06141</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.40895</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.07234</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.30057</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.73011</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.91982</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.19634</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.8642</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33.8765</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.73172</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.69781</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.65729</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.68555</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33.71612</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17.02385</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.16133</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.60606</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.09345</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.21918</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.45196</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.89253</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.42233</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.43603</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.10996</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.54795</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.61626</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.08917</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.67324</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.05003</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.67423</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.82928</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.2976</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.94238</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.13636</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.10856</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.86086</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.65825</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.57627</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.40613</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.37354</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.00925</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.23279</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.07681</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.81634</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.61419</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.09999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.60723</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.11365</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.60856</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.10953</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.60941</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.09853</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.60084</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.10842</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6004699999999999</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.14203</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.60137</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.12022</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60528</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.09691</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6170099999999999</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.11342</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.6087900000000001</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.11795</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.60487</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.11983</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.60037</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.09924</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.61088</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.11143</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.61166</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.11382</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.60681</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.10061</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.6024</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.11191</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.60165</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.11463</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.59565</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.11866</v>
       </c>
     </row>
   </sheetData>
